--- a/Table/D_地区表.xlsx
+++ b/Table/D_地区表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28007"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Unity\BFramework-Ex\Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\BFramework-Ex\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F74513F-8515-4481-90C7-19B08B65061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18D65B1-03BD-47EB-9032-FEEE0F2B97A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6156" yWindow="4200" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tb_region" sheetId="1" r:id="rId1"/>
@@ -28,16 +28,9 @@
     <t>string</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
-    <t>region</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>地区</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -62,10 +55,6 @@
     <t>地区3</t>
   </si>
   <si>
-    <t>test1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -90,10 +79,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>test2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2,3,4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -101,10 +86,6 @@
     <t>array_long</t>
   </si>
   <si>
-    <t>test3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -116,17 +97,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>test4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>composite_string</t>
   </si>
   <si>
-    <t>test5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,10 +131,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>test6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>array_int</t>
   </si>
   <si>
@@ -184,14 +153,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>test7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>test8</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>测试8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -204,6 +165,46 @@
   </si>
   <si>
     <t>4,5,5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Region</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -559,34 +560,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -597,94 +598,94 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2"/>
     </row>
@@ -693,31 +694,31 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -725,31 +726,31 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -757,36 +758,36 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -794,14 +795,11 @@
     <sortCondition ref="B7:B8"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:J1" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"S,C,S|C,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:H2" xr:uid="{321E066E-77F6-4EED-8B34-BD87B83FAC81}">
-      <formula1>"int,long,float,string,vector2,vector3,array_string,array_int,array_long,array_float,composite_string,composite_int"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:J2" xr:uid="{0DFA344A-1BD5-4396-A53D-117E4CC14CA9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:J2" xr:uid="{321E066E-77F6-4EED-8B34-BD87B83FAC81}">
       <formula1>"int,long,float,string,vector2,vector3,array_string,array_int,array_long,array_float,composite_string,composite_int"</formula1>
     </dataValidation>
   </dataValidations>
